--- a/gestione_coordinate_pois.xlsx
+++ b/gestione_coordinate_pois.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\Quadrilatero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC52A0F-D7C4-4499-9125-543ED67711FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7147534E-D975-45AC-AE2E-87E40D4635AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -433,6 +446,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="6" max="6" width="11" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -465,7 +481,7 @@
         <v>44.49911485308791</v>
       </c>
       <c r="C2">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D2">
         <v>44.49911485308791</v>
@@ -474,7 +490,7 @@
         <v>11.33668386365537</v>
       </c>
       <c r="F2">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G2">
         <v>11.33668386365537</v>
@@ -488,7 +504,7 @@
         <v>44.498944000000002</v>
       </c>
       <c r="C3">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D3">
         <v>44.498944000000002</v>
@@ -497,7 +513,7 @@
         <v>11.340329000000001</v>
       </c>
       <c r="F3">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G3">
         <v>11.340329000000001</v>
@@ -511,7 +527,7 @@
         <v>44.50018</v>
       </c>
       <c r="C4">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D4">
         <v>44.50018</v>
@@ -520,7 +536,7 @@
         <v>11.33807</v>
       </c>
       <c r="F4">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G4">
         <v>11.33807</v>
@@ -534,7 +550,7 @@
         <v>44.498063683720687</v>
       </c>
       <c r="C5">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D5">
         <v>44.498063683720687</v>
@@ -543,7 +559,7 @@
         <v>11.341926289317311</v>
       </c>
       <c r="F5">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G5">
         <v>11.341926289317311</v>
@@ -557,7 +573,7 @@
         <v>44.500663888888901</v>
       </c>
       <c r="C6">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D6">
         <v>44.500663888888901</v>
@@ -566,7 +582,7 @@
         <v>11.340769444444399</v>
       </c>
       <c r="F6">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G6">
         <v>11.340769444444399</v>
@@ -580,7 +596,7 @@
         <v>44.50018</v>
       </c>
       <c r="C7">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D7">
         <v>44.499899999999997</v>
@@ -589,7 +605,7 @@
         <v>11.339986</v>
       </c>
       <c r="F7">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G7">
         <v>11.3399</v>
@@ -603,7 +619,7 @@
         <v>44.499997222222198</v>
       </c>
       <c r="C8">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D8">
         <v>44.499997222222198</v>
@@ -612,7 +628,7 @@
         <v>11.340388888888899</v>
       </c>
       <c r="F8">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G8">
         <v>11.340388888888899</v>
@@ -626,7 +642,7 @@
         <v>44.499252779999999</v>
       </c>
       <c r="C9">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D9">
         <v>44.499252779999999</v>
@@ -635,7 +651,7 @@
         <v>11.34074444</v>
       </c>
       <c r="F9">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G9">
         <v>11.34074444</v>
@@ -649,7 +665,7 @@
         <v>44.501514</v>
       </c>
       <c r="C10">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D10">
         <v>44.501514</v>
@@ -658,7 +674,7 @@
         <v>11.343557000000001</v>
       </c>
       <c r="F10">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G10">
         <v>11.343557000000001</v>
@@ -672,7 +688,7 @@
         <v>44.498899000000002</v>
       </c>
       <c r="C11">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D11">
         <v>44.498899000000002</v>
@@ -681,7 +697,7 @@
         <v>11.342153</v>
       </c>
       <c r="F11">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G11">
         <v>11.342153</v>
@@ -695,7 +711,7 @@
         <v>44.498899000000002</v>
       </c>
       <c r="C12">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D12">
         <v>44.498899000000002</v>
@@ -704,7 +720,7 @@
         <v>11.342241</v>
       </c>
       <c r="F12">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G12">
         <v>11.342241</v>
@@ -718,7 +734,7 @@
         <v>44.499068999999999</v>
       </c>
       <c r="C13">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D13">
         <v>44.499068999999999</v>
@@ -727,7 +743,7 @@
         <v>11.341809</v>
       </c>
       <c r="F13">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G13">
         <v>11.341809</v>
@@ -741,7 +757,7 @@
         <v>44.499079999999999</v>
       </c>
       <c r="C14">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D14">
         <v>44.499079999999999</v>
@@ -750,7 +766,7 @@
         <v>11.342241100000001</v>
       </c>
       <c r="F14">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G14">
         <v>11.342241100000001</v>
@@ -764,7 +780,7 @@
         <v>44.501248758211673</v>
       </c>
       <c r="C15">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D15">
         <v>44.501248758211673</v>
@@ -773,11 +789,14 @@
         <v>11.34075366622929</v>
       </c>
       <c r="F15">
-        <v>-8.6000000000000003E-5</v>
+        <v>-8.0000000000000007E-5</v>
       </c>
       <c r="G15">
         <v>11.34075366622929</v>
       </c>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C20" s="1"/>
     </row>
     <row r="23" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C23" s="1"/>

--- a/gestione_coordinate_pois.xlsx
+++ b/gestione_coordinate_pois.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\Quadrilatero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7147534E-D975-45AC-AE2E-87E40D4635AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5012E5-0BF3-43B8-B824-AA4873B9CB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11556" yWindow="216" windowWidth="15708" windowHeight="11856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -447,6 +447,7 @@
   <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="12.6640625" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
@@ -481,7 +482,7 @@
         <v>44.49911485308791</v>
       </c>
       <c r="C2">
-        <v>-2.0000000000000001E-4</v>
+        <v>-2.5000000000000001E-4</v>
       </c>
       <c r="D2">
         <v>44.49911485308791</v>
@@ -527,7 +528,7 @@
         <v>44.50018</v>
       </c>
       <c r="C4">
-        <v>-2.0000000000000001E-4</v>
+        <v>-1.9000000000000001E-4</v>
       </c>
       <c r="D4">
         <v>44.50018</v>
@@ -619,7 +620,7 @@
         <v>44.499997222222198</v>
       </c>
       <c r="C8">
-        <v>-2.0000000000000001E-4</v>
+        <v>-1.7000000000000001E-4</v>
       </c>
       <c r="D8">
         <v>44.499997222222198</v>
@@ -628,7 +629,7 @@
         <v>11.340388888888899</v>
       </c>
       <c r="F8">
-        <v>-8.0000000000000007E-5</v>
+        <v>-7.8999999999999996E-5</v>
       </c>
       <c r="G8">
         <v>11.340388888888899</v>
@@ -642,7 +643,7 @@
         <v>44.499252779999999</v>
       </c>
       <c r="C9">
-        <v>-2.0000000000000001E-4</v>
+        <v>-1E-4</v>
       </c>
       <c r="D9">
         <v>44.499252779999999</v>
@@ -651,7 +652,7 @@
         <v>11.34074444</v>
       </c>
       <c r="F9">
-        <v>-8.0000000000000007E-5</v>
+        <v>-7.8999999999999996E-5</v>
       </c>
       <c r="G9">
         <v>11.34074444</v>

--- a/gestione_coordinate_pois.xlsx
+++ b/gestione_coordinate_pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\Quadrilatero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB5012E5-0BF3-43B8-B824-AA4873B9CB74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647918A0-FA25-4C0E-A615-728E89CA2A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11556" yWindow="216" windowWidth="15708" windowHeight="11856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -574,7 +574,7 @@
         <v>44.500663888888901</v>
       </c>
       <c r="C6">
-        <v>-2.0000000000000001E-4</v>
+        <v>-1.8000000000000001E-4</v>
       </c>
       <c r="D6">
         <v>44.500663888888901</v>
@@ -652,7 +652,7 @@
         <v>11.34074444</v>
       </c>
       <c r="F9">
-        <v>-7.8999999999999996E-5</v>
+        <v>-7.6000000000000004E-5</v>
       </c>
       <c r="G9">
         <v>11.34074444</v>

--- a/gestione_coordinate_pois.xlsx
+++ b/gestione_coordinate_pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\Quadrilatero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647918A0-FA25-4C0E-A615-728E89CA2A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E983188-9F7B-4B59-8DC4-9663C41B1D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11556" yWindow="216" windowWidth="15708" windowHeight="11856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -571,7 +571,7 @@
         <v>11</v>
       </c>
       <c r="B6">
-        <v>44.500663888888901</v>
+        <v>44.50065</v>
       </c>
       <c r="C6">
         <v>-1.8000000000000001E-4</v>
@@ -583,7 +583,7 @@
         <v>11.340769444444399</v>
       </c>
       <c r="F6">
-        <v>-8.0000000000000007E-5</v>
+        <v>-7.8999999999999996E-5</v>
       </c>
       <c r="G6">
         <v>11.340769444444399</v>

--- a/gestione_coordinate_pois.xlsx
+++ b/gestione_coordinate_pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\Quadrilatero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E983188-9F7B-4B59-8DC4-9663C41B1D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF11364C-FB87-4288-AD79-8F45B74A395B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11556" yWindow="216" windowWidth="15708" windowHeight="11856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -583,7 +583,7 @@
         <v>11.340769444444399</v>
       </c>
       <c r="F6">
-        <v>-7.8999999999999996E-5</v>
+        <v>-7.6000000000000004E-5</v>
       </c>
       <c r="G6">
         <v>11.340769444444399</v>

--- a/gestione_coordinate_pois.xlsx
+++ b/gestione_coordinate_pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\Quadrilatero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF11364C-FB87-4288-AD79-8F45B74A395B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05FFBC4C-9ECA-4D02-88A4-69CDAE5B2D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11556" yWindow="216" windowWidth="15708" windowHeight="11856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -574,7 +574,7 @@
         <v>44.50065</v>
       </c>
       <c r="C6">
-        <v>-1.8000000000000001E-4</v>
+        <v>-1.7000000000000001E-4</v>
       </c>
       <c r="D6">
         <v>44.500663888888901</v>
@@ -583,7 +583,7 @@
         <v>11.340769444444399</v>
       </c>
       <c r="F6">
-        <v>-7.6000000000000004E-5</v>
+        <v>-6.9999999999999994E-5</v>
       </c>
       <c r="G6">
         <v>11.340769444444399</v>

--- a/gestione_coordinate_pois.xlsx
+++ b/gestione_coordinate_pois.xlsx
@@ -463,19 +463,19 @@
         <v>44.49911485308791</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.00025</v>
+        <v>-0.00035</v>
       </c>
       <c r="D2" t="n">
-        <v>44.49886485308791</v>
+        <v>44.49876485308791</v>
       </c>
       <c r="E2" t="n">
         <v>11.33668386365537</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.000000000000001e-05</v>
+        <v>-8.2e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>11.33660386365537</v>
+        <v>11.33660186365537</v>
       </c>
     </row>
     <row r="3">

--- a/gestione_coordinate_pois.xlsx
+++ b/gestione_coordinate_pois.xlsx
@@ -463,19 +463,19 @@
         <v>44.49911485308791</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.00035</v>
+        <v>-0.00039</v>
       </c>
       <c r="D2" t="n">
-        <v>44.49876485308791</v>
+        <v>44.49872485308791</v>
       </c>
       <c r="E2" t="n">
         <v>11.33668386365537</v>
       </c>
       <c r="F2" t="n">
-        <v>-8.2e-05</v>
+        <v>-6.999999999999999e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>11.33660186365537</v>
+        <v>11.33661386365537</v>
       </c>
     </row>
     <row r="3">

--- a/gestione_coordinate_pois.xlsx
+++ b/gestione_coordinate_pois.xlsx
@@ -472,10 +472,10 @@
         <v>11.33668386365537</v>
       </c>
       <c r="F2" t="n">
-        <v>-6.999999999999999e-05</v>
+        <v>-6e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>11.33661386365537</v>
+        <v>11.33662386365537</v>
       </c>
     </row>
     <row r="3">

--- a/gestione_coordinate_pois.xlsx
+++ b/gestione_coordinate_pois.xlsx
@@ -597,10 +597,10 @@
         <v>11.339986</v>
       </c>
       <c r="F7" t="n">
-        <v>-8.000000000000001e-05</v>
+        <v>-0.0001</v>
       </c>
       <c r="G7" t="n">
-        <v>11.339906</v>
+        <v>11.339886</v>
       </c>
     </row>
     <row r="8">

--- a/gestione_coordinate_pois.xlsx
+++ b/gestione_coordinate_pois.xlsx
@@ -588,19 +588,19 @@
         <v>44.50018</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0002</v>
+        <v>-0.00025</v>
       </c>
       <c r="D7" t="n">
-        <v>44.49998</v>
+        <v>44.49993</v>
       </c>
       <c r="E7" t="n">
         <v>11.339986</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.0001</v>
+        <v>-0.00013</v>
       </c>
       <c r="G7" t="n">
-        <v>11.339886</v>
+        <v>11.339856</v>
       </c>
     </row>
     <row r="8">

--- a/gestione_coordinate_pois.xlsx
+++ b/gestione_coordinate_pois.xlsx
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>44.50018</v>
+        <v>44.50004</v>
       </c>
       <c r="C7" t="n">
         <v>-0.00025</v>
       </c>
       <c r="D7" t="n">
-        <v>44.49993</v>
+        <v>44.49979</v>
       </c>
       <c r="E7" t="n">
-        <v>11.339986</v>
+        <v>11.339782</v>
       </c>
       <c r="F7" t="n">
         <v>-0.00013</v>
       </c>
       <c r="G7" t="n">
-        <v>11.339856</v>
+        <v>11.339652</v>
       </c>
     </row>
     <row r="8">

--- a/gestione_coordinate_pois.xlsx
+++ b/gestione_coordinate_pois.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\Quadrilatero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1E4EB1F-CEAC-4E27-8E53-DB1BB8282A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97F8D367-20D4-4559-B3A4-B60FE2499864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12888" yWindow="0" windowWidth="10152" windowHeight="11856" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -571,7 +571,7 @@
         <v>44.500039999999998</v>
       </c>
       <c r="C7">
-        <v>-2.7999999999999998E-4</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="D7">
         <v>44.499789999999997</v>
@@ -583,7 +583,7 @@
         <v>-1.4999999999999999E-4</v>
       </c>
       <c r="G7">
-        <v>11.339651999999999</v>
+        <v>11.339632</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">

--- a/gestione_coordinate_pois.xlsx
+++ b/gestione_coordinate_pois.xlsx
@@ -588,10 +588,10 @@
         <v>44.50004</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0002</v>
+        <v>-0.00015</v>
       </c>
       <c r="D7" t="n">
-        <v>44.49984</v>
+        <v>44.49989</v>
       </c>
       <c r="E7" t="n">
         <v>11.339782</v>
